--- a/outputs/resultats/bmo/2026_t1_vs_2025_t3/comparison.xlsx
+++ b/outputs/resultats/bmo/2026_t1_vs_2025_t3/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +45,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEBD0"/>
+        <bgColor rgb="00FDEBD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,10 +72,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -450,6 +462,9 @@
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,9 +523,1192 @@
           <t>Commentaire analyste</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut validation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Validé par</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Validé le</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>TABLEAU 13</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Des détails sur les billets à moyen terme sont présentés à la note 16 des états financiers consolidés audités du Rapport annuel de BMO pour 2024. La note 16 des états financiers consolidés audités et la note 17 des états financiers consolidés annuels audités du Rapport annuel de BMO pour 2024, traitent en détail du capital social et des autres instruments de capitaux propres.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Des détails sur les billets à moyen terme sont présentés à la note 16 des états financiers consolidés audités du Rapport annuel de BMO pour 2025. La note 16 des états financiers consolidés annuels audités du Rapport annuel de BMO pour 2025, traitent en détail du capital social et des autres instruments convertibles en actions ordinaires.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>La modification de cette note clarifie que les instruments sont convertibles en actions ordinaires, ce qui peut avoir un impact sur la compréhension des investisseurs quant à la structure du capital.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TABLEAU 13</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Convertible en actions ordinaires. Les billets avec remboursement de capital à recours limité sont convertibles en actions ordinaires en vertu du recours aux actions privilégiées, série 49, aux actions privilégiées, série 51, aux actions privilégiées, série 53, aux actions privilégiées, série 54 et aux actions privilégiées, à recours limité, série 1, série 2, série 3, série 4, série 5 et série 6, respectivement émises en même temps que les billets avec remboursement de capital à recours limité, actuellement les actifs détenus dans une fiducie à recours limité.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Convertible en actions ordinaires. Les billets avec remboursement de capital à recours limité sont convertibles en actions ordinaires en vertu du recours aux actions privilégiées, série 51, aux actions privilégiées, série 53, aux actions privilégiées, série 54 et aux actions privilégiées, série 55 au titre des billets avec remboursement de capital à recours limité, série 4, série 5 et série 6, respectivement émises en même temps que les billets avec remboursement de capital à recours limité, qui comprennent actions privilégiées, série 51, aux actions privilégiées, série 53, aux actions privilégiées, série 54 et aux actions privilégiées, série 55 au titre des billets avec remboursement de capital à recours limité, série 4, série 5 et série 6, respectivement émises en même temps que les billets avec remboursement de capital à recours limité.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>La reformulation de cette note précise les séries d'actions privilégiées concernées, ce qui est crucial pour la compréhension des droits de conversion des investisseurs.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>TABLEAU 13</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Billets avec remboursement de capital à recours limité, série 1 à 4,300 %</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>La suppression de cette série de billets peut refléter un changement dans la stratégie de financement ou dans les conditions de marché affectant les instruments de dette.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Réglementation</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>TABLEAU 22</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Le ratio prêt/valeur (RPV) est fonction de l’encours initial des prêts hypothécaires et des montants autorisés pouvant être prélevés sur les marges de crédit sur valeur domiciliaire, divisés par la valeur de la garantie au moment du montage.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Cette note a été ajoutée pour clarifier le calcul du ratio prêt/valeur, ce qui est essentiel pour l'évaluation des risques liés aux prêts hypothécaires.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 25</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 25</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 26</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 26</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 27</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 27</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 28</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 28</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 29</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 29</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 30</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 30</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 31</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 31</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 32</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 32</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 33</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 33</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 34</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 34</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 35</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 35</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 37</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 37</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 38</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 38</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 39</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 39</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 40</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 40</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 41</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 41</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Réglementation</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Réglementation</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 21</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 21</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Réglementation</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 24</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU 24</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:N25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>